--- a/exports/KEI_full_report.xlsx
+++ b/exports/KEI_full_report.xlsx
@@ -18,9 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd"/>
+    <numFmt numFmtId="167" formatCode="YYYY-MM-DD"/>
   </numFmts>
   <fonts count="1">
     <font>
@@ -51,10 +53,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -420,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q65"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -509,6 +512,26 @@
           <t>candles_held</t>
         </is>
       </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>expiry</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>reached_expiry</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>rule_trades</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>rule_wins</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -534,28 +557,28 @@
         <v>4.94</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>44582.55208333334</v>
+        <v>44585.38541666666</v>
       </c>
       <c r="H2" t="n">
-        <v>1180</v>
+        <v>1113.5</v>
       </c>
       <c r="I2" t="n">
         <v>1121.643898479982</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>11.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K2" t="n">
-        <v>7.13</v>
+        <v>1.09</v>
       </c>
       <c r="L2" t="n">
         <v>0.77</v>
       </c>
       <c r="M2" t="n">
-        <v>1.05</v>
+        <v>2.97</v>
       </c>
       <c r="N2" t="n">
-        <v>3.28</v>
+        <v>5.1</v>
       </c>
       <c r="O2" t="n">
         <v>1.79</v>
@@ -564,7 +587,19 @@
         <v>0</v>
       </c>
       <c r="Q2" t="n">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="R2" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S2" t="b">
+        <v>0</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -591,22 +626,22 @@
         <v>11.87</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>44637.38541666666</v>
+        <v>44637.55208333334</v>
       </c>
       <c r="H3" t="n">
-        <v>1043.5</v>
+        <v>1100</v>
       </c>
       <c r="I3" t="n">
         <v>1066.488129487021</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>52</v>
+        <v>52.16666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>6.29</v>
+        <v>1.21</v>
       </c>
       <c r="L3" t="n">
-        <v>4.12</v>
+        <v>7.22</v>
       </c>
       <c r="M3" t="n">
         <v>4.29</v>
@@ -621,7 +656,19 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>73</v>
+        <v>74</v>
+      </c>
+      <c r="R3" s="3" t="n">
+        <v>44588</v>
+      </c>
+      <c r="S3" t="b">
+        <v>1</v>
+      </c>
+      <c r="T3" t="n">
+        <v>3</v>
+      </c>
+      <c r="U3" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -648,19 +695,19 @@
         <v>9.76</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>44670.38541666666</v>
+        <v>44670.55208333334</v>
       </c>
       <c r="H4" t="n">
-        <v>1250</v>
+        <v>1178</v>
       </c>
       <c r="I4" t="n">
         <v>1189.443661938665</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>32.83333333333334</v>
+        <v>33</v>
       </c>
       <c r="K4" t="n">
-        <v>13.64</v>
+        <v>7.09</v>
       </c>
       <c r="L4" t="n">
         <v>5.45</v>
@@ -678,7 +725,19 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R4" s="3" t="n">
+        <v>44651</v>
+      </c>
+      <c r="S4" t="b">
+        <v>1</v>
+      </c>
+      <c r="T4" t="n">
+        <v>2</v>
+      </c>
+      <c r="U4" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="5">
@@ -705,19 +764,19 @@
         <v>12.65</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>44697.55208333334</v>
+        <v>44698.38541666666</v>
       </c>
       <c r="H5" t="n">
-        <v>1150</v>
+        <v>1215.1</v>
       </c>
       <c r="I5" t="n">
         <v>1179.843145578906</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>27</v>
+        <v>27.83333333333333</v>
       </c>
       <c r="K5" t="n">
-        <v>2.38</v>
+        <v>-3.15</v>
       </c>
       <c r="L5" t="n">
         <v>8.81</v>
@@ -735,7 +794,19 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>37</v>
+        <v>38</v>
+      </c>
+      <c r="R5" s="3" t="n">
+        <v>44679</v>
+      </c>
+      <c r="S5" t="b">
+        <v>1</v>
+      </c>
+      <c r="T5" t="n">
+        <v>2</v>
+      </c>
+      <c r="U5" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="6">
@@ -762,28 +833,28 @@
         <v>14.03</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>44705.55208333334</v>
+        <v>44706.38541666666</v>
       </c>
       <c r="H6" t="n">
-        <v>1195.7</v>
+        <v>1130.2</v>
       </c>
       <c r="I6" t="n">
         <v>1134.640951210213</v>
       </c>
       <c r="J6" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.6</v>
+        <v>-6.99</v>
       </c>
       <c r="L6" t="n">
-        <v>6.18</v>
+        <v>7.47</v>
       </c>
       <c r="M6" t="n">
         <v>3.37</v>
       </c>
       <c r="N6" t="n">
-        <v>1.99</v>
+        <v>6.87</v>
       </c>
       <c r="O6" t="n">
         <v>5.83</v>
@@ -792,7 +863,19 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R6" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S6" t="b">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -819,25 +902,25 @@
         <v>13.19</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>44708.55208333334</v>
+        <v>44711.38541666666</v>
       </c>
       <c r="H7" t="n">
-        <v>1208</v>
+        <v>1234</v>
       </c>
       <c r="I7" t="n">
         <v>1227.810128219882</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>2.166666666666667</v>
+        <v>5</v>
       </c>
       <c r="K7" t="n">
-        <v>-6.88</v>
+        <v>-9.18</v>
       </c>
       <c r="L7" t="n">
-        <v>7.06</v>
+        <v>10.36</v>
       </c>
       <c r="M7" t="n">
-        <v>2.35</v>
+        <v>2.36</v>
       </c>
       <c r="N7" t="n">
         <v>5.71</v>
@@ -849,7 +932,19 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>6</v>
+        <v>7</v>
+      </c>
+      <c r="R7" s="3" t="n">
+        <v>44707</v>
+      </c>
+      <c r="S7" t="b">
+        <v>1</v>
+      </c>
+      <c r="T7" t="n">
+        <v>2</v>
+      </c>
+      <c r="U7" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
@@ -876,22 +971,22 @@
         <v>8.92</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>44729.38541666666</v>
+        <v>44729.55208333334</v>
       </c>
       <c r="H8" t="n">
-        <v>1218</v>
+        <v>1190</v>
       </c>
       <c r="I8" t="n">
         <v>1212.005129431581</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>18</v>
+        <v>18.16666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>-1.3</v>
+        <v>-3.57</v>
       </c>
       <c r="L8" t="n">
-        <v>1.7</v>
+        <v>4.3</v>
       </c>
       <c r="M8" t="n">
         <v>1.85</v>
@@ -906,7 +1001,19 @@
         <v>0</v>
       </c>
       <c r="Q8" t="n">
-        <v>29</v>
+        <v>30</v>
+      </c>
+      <c r="R8" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S8" t="b">
+        <v>0</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -933,19 +1040,19 @@
         <v>9.949999999999999</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>44747.55208333334</v>
+        <v>44748.38541666666</v>
       </c>
       <c r="H9" t="n">
-        <v>1217.2</v>
+        <v>1239.4</v>
       </c>
       <c r="I9" t="n">
         <v>1230.351840571321</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>18</v>
+        <v>18.83333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>-2.29</v>
+        <v>-4.15</v>
       </c>
       <c r="L9" t="n">
         <v>5.71</v>
@@ -963,7 +1070,19 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>25</v>
+        <v>26</v>
+      </c>
+      <c r="R9" s="3" t="n">
+        <v>44742</v>
+      </c>
+      <c r="S9" t="b">
+        <v>1</v>
+      </c>
+      <c r="T9" t="n">
+        <v>2</v>
+      </c>
+      <c r="U9" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="10">
@@ -990,19 +1109,19 @@
         <v>8.630000000000001</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>44826.55208333334</v>
+        <v>44827.38541666666</v>
       </c>
       <c r="H10" t="n">
-        <v>1491.5</v>
+        <v>1445.5</v>
       </c>
       <c r="I10" t="n">
         <v>1489.493416841652</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>78.16666666666667</v>
+        <v>79</v>
       </c>
       <c r="K10" t="n">
-        <v>20.34</v>
+        <v>16.63</v>
       </c>
       <c r="L10" t="n">
         <v>6.81</v>
@@ -1020,7 +1139,19 @@
         <v>0</v>
       </c>
       <c r="Q10" t="n">
-        <v>108</v>
+        <v>109</v>
+      </c>
+      <c r="R10" s="3" t="n">
+        <v>44770</v>
+      </c>
+      <c r="S10" t="b">
+        <v>1</v>
+      </c>
+      <c r="T10" t="n">
+        <v>3</v>
+      </c>
+      <c r="U10" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -1047,28 +1178,28 @@
         <v>9.140000000000001</v>
       </c>
       <c r="G11" s="1" t="n">
-        <v>44851.55208333334</v>
+        <v>44852.38541666666</v>
       </c>
       <c r="H11" t="n">
-        <v>1464</v>
+        <v>1495</v>
       </c>
       <c r="I11" t="n">
         <v>1483.58992963191</v>
       </c>
       <c r="J11" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K11" t="n">
-        <v>-1.28</v>
+        <v>-3.42</v>
       </c>
       <c r="L11" t="n">
-        <v>2.94</v>
+        <v>4.19</v>
       </c>
       <c r="M11" t="n">
         <v>2.55</v>
       </c>
       <c r="N11" t="n">
-        <v>1.74</v>
+        <v>2.12</v>
       </c>
       <c r="O11" t="n">
         <v>-2.99</v>
@@ -1077,7 +1208,19 @@
         <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R11" s="3" t="n">
+        <v>44833</v>
+      </c>
+      <c r="S11" t="b">
+        <v>1</v>
+      </c>
+      <c r="T11" t="n">
+        <v>2</v>
+      </c>
+      <c r="U11" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="12">
@@ -1104,19 +1247,19 @@
         <v>6.93</v>
       </c>
       <c r="G12" s="1" t="n">
-        <v>44908.38541666666</v>
+        <v>44908.55208333334</v>
       </c>
       <c r="H12" t="n">
-        <v>1536</v>
+        <v>1525</v>
       </c>
       <c r="I12" t="n">
         <v>1525.965949811443</v>
       </c>
       <c r="J12" s="2" t="n">
-        <v>56</v>
+        <v>56.16666666666666</v>
       </c>
       <c r="K12" t="n">
-        <v>2.74</v>
+        <v>2.01</v>
       </c>
       <c r="L12" t="n">
         <v>2.47</v>
@@ -1134,7 +1277,19 @@
         <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R12" s="3" t="n">
+        <v>44861</v>
+      </c>
+      <c r="S12" t="b">
+        <v>1</v>
+      </c>
+      <c r="T12" t="n">
+        <v>3</v>
+      </c>
+      <c r="U12" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="13">
@@ -1161,25 +1316,25 @@
         <v>6.75</v>
       </c>
       <c r="G13" s="1" t="n">
-        <v>44921.55208333334</v>
+        <v>44922.38541666666</v>
       </c>
       <c r="H13" t="n">
-        <v>1488.9</v>
+        <v>1514.2</v>
       </c>
       <c r="I13" t="n">
         <v>1510.04009853164</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>13</v>
+        <v>13.83333333333333</v>
       </c>
       <c r="K13" t="n">
-        <v>2.37</v>
+        <v>0.71</v>
       </c>
       <c r="L13" t="n">
         <v>1.51</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4</v>
+        <v>0.75</v>
       </c>
       <c r="N13" t="n">
         <v>5.6</v>
@@ -1191,7 +1346,19 @@
         <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R13" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S13" t="b">
+        <v>0</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="14">
@@ -1218,25 +1385,25 @@
         <v>9.59</v>
       </c>
       <c r="G14" s="1" t="n">
-        <v>44971.55208333334</v>
+        <v>44972.38541666666</v>
       </c>
       <c r="H14" t="n">
-        <v>1609.9</v>
+        <v>1591.2</v>
       </c>
       <c r="I14" t="n">
         <v>1599.385262580024</v>
       </c>
       <c r="J14" s="2" t="n">
-        <v>49.16666666666666</v>
+        <v>50</v>
       </c>
       <c r="K14" t="n">
-        <v>6.32</v>
+        <v>5.09</v>
       </c>
       <c r="L14" t="n">
         <v>6.81</v>
       </c>
       <c r="M14" t="n">
-        <v>0.93</v>
+        <v>1.74</v>
       </c>
       <c r="N14" t="n">
         <v>3.11</v>
@@ -1248,7 +1415,19 @@
         <v>0</v>
       </c>
       <c r="Q14" t="n">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="R14" s="3" t="n">
+        <v>44924</v>
+      </c>
+      <c r="S14" t="b">
+        <v>1</v>
+      </c>
+      <c r="T14" t="n">
+        <v>3</v>
+      </c>
+      <c r="U14" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="15">
@@ -1275,22 +1454,22 @@
         <v>6.27</v>
       </c>
       <c r="G15" s="1" t="n">
-        <v>44973.55208333334</v>
+        <v>44974.38541666666</v>
       </c>
       <c r="H15" t="n">
-        <v>1679.9</v>
+        <v>1700.25</v>
       </c>
       <c r="I15" t="n">
         <v>1690.923942709056</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>2</v>
       </c>
       <c r="K15" t="n">
-        <v>-5.57</v>
+        <v>-6.85</v>
       </c>
       <c r="L15" t="n">
-        <v>5.89</v>
+        <v>7.95</v>
       </c>
       <c r="M15" t="n">
         <v>0</v>
@@ -1305,7 +1484,19 @@
         <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R15" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S15" t="b">
+        <v>0</v>
+      </c>
+      <c r="T15" t="n">
+        <v>1</v>
+      </c>
+      <c r="U15" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="16">
@@ -1332,28 +1523,28 @@
         <v>7.27</v>
       </c>
       <c r="G16" s="1" t="n">
-        <v>44995.55208333334</v>
+        <v>44998.38541666666</v>
       </c>
       <c r="H16" t="n">
-        <v>1646.95</v>
+        <v>1594.2</v>
       </c>
       <c r="I16" t="n">
         <v>1617.576985497545</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K16" t="n">
-        <v>-3.13</v>
+        <v>-6.24</v>
       </c>
       <c r="L16" t="n">
-        <v>5.68</v>
+        <v>8.58</v>
       </c>
       <c r="M16" t="n">
-        <v>0.93</v>
+        <v>2.84</v>
       </c>
       <c r="N16" t="n">
-        <v>1.99</v>
+        <v>4.37</v>
       </c>
       <c r="O16" t="n">
         <v>0.78</v>
@@ -1362,7 +1553,19 @@
         <v>0</v>
       </c>
       <c r="Q16" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R16" s="3" t="n">
+        <v>44980</v>
+      </c>
+      <c r="S16" t="b">
+        <v>1</v>
+      </c>
+      <c r="T16" t="n">
+        <v>2</v>
+      </c>
+      <c r="U16" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="17">
@@ -1389,22 +1592,22 @@
         <v>7.41</v>
       </c>
       <c r="G17" s="1" t="n">
-        <v>45013.55208333334</v>
+        <v>45014.38541666666</v>
       </c>
       <c r="H17" t="n">
-        <v>1675</v>
+        <v>1722.4</v>
       </c>
       <c r="I17" t="n">
         <v>1684.040383439585</v>
       </c>
       <c r="J17" s="2" t="n">
-        <v>15.16666666666667</v>
+        <v>16</v>
       </c>
       <c r="K17" t="n">
-        <v>-5.07</v>
+        <v>-8.039999999999999</v>
       </c>
       <c r="L17" t="n">
-        <v>6.15</v>
+        <v>8.460000000000001</v>
       </c>
       <c r="M17" t="n">
         <v>1.32</v>
@@ -1419,7 +1622,19 @@
         <v>1</v>
       </c>
       <c r="Q17" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R17" s="3" t="n">
+        <v>45014</v>
+      </c>
+      <c r="S17" t="b">
+        <v>0</v>
+      </c>
+      <c r="T17" t="n">
+        <v>1</v>
+      </c>
+      <c r="U17" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="18">
@@ -1446,19 +1661,19 @@
         <v>7.42</v>
       </c>
       <c r="G18" s="1" t="n">
-        <v>45135.55208333334</v>
+        <v>45138.38541666666</v>
       </c>
       <c r="H18" t="n">
-        <v>2440</v>
+        <v>2407.9</v>
       </c>
       <c r="I18" t="n">
         <v>2421.795644140334</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>121.1666666666667</v>
+        <v>124</v>
       </c>
       <c r="K18" t="n">
-        <v>41.66</v>
+        <v>39.8</v>
       </c>
       <c r="L18" t="n">
         <v>3.53</v>
@@ -1476,7 +1691,19 @@
         <v>0</v>
       </c>
       <c r="Q18" t="n">
-        <v>164</v>
+        <v>165</v>
+      </c>
+      <c r="R18" s="3" t="n">
+        <v>45043</v>
+      </c>
+      <c r="S18" t="b">
+        <v>1</v>
+      </c>
+      <c r="T18" t="n">
+        <v>5</v>
+      </c>
+      <c r="U18" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="19">
@@ -1503,19 +1730,19 @@
         <v>9.609999999999999</v>
       </c>
       <c r="G19" s="1" t="n">
-        <v>45154.55208333334</v>
+        <v>45155.38541666666</v>
       </c>
       <c r="H19" t="n">
-        <v>2363</v>
+        <v>2441.9</v>
       </c>
       <c r="I19" t="n">
         <v>2421.284716762705</v>
       </c>
       <c r="J19" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K19" t="n">
-        <v>1.86</v>
+        <v>-1.41</v>
       </c>
       <c r="L19" t="n">
         <v>3.32</v>
@@ -1533,7 +1760,19 @@
         <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>24</v>
+        <v>25</v>
+      </c>
+      <c r="R19" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S19" t="b">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1</v>
+      </c>
+      <c r="U19" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1560,19 +1799,19 @@
         <v>9.18</v>
       </c>
       <c r="G20" s="1" t="n">
-        <v>45175.55208333334</v>
+        <v>45176.38541666666</v>
       </c>
       <c r="H20" t="n">
-        <v>2569</v>
+        <v>2555.65</v>
       </c>
       <c r="I20" t="n">
         <v>2568.570143206964</v>
       </c>
       <c r="J20" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K20" t="n">
-        <v>5.2</v>
+        <v>4.66</v>
       </c>
       <c r="L20" t="n">
         <v>3.76</v>
@@ -1590,7 +1829,19 @@
         <v>0</v>
       </c>
       <c r="Q20" t="n">
-        <v>30</v>
+        <v>31</v>
+      </c>
+      <c r="R20" s="3" t="n">
+        <v>45169</v>
+      </c>
+      <c r="S20" t="b">
+        <v>1</v>
+      </c>
+      <c r="T20" t="n">
+        <v>2</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="21">
@@ -1617,19 +1868,19 @@
         <v>6.05</v>
       </c>
       <c r="G21" s="1" t="n">
-        <v>45195.55208333334</v>
+        <v>45196.38541666666</v>
       </c>
       <c r="H21" t="n">
-        <v>2525</v>
+        <v>2595</v>
       </c>
       <c r="I21" t="n">
         <v>2594.650484855953</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>19.16666666666667</v>
+        <v>20</v>
       </c>
       <c r="K21" t="n">
-        <v>1.2</v>
+        <v>-1.54</v>
       </c>
       <c r="L21" t="n">
         <v>4.97</v>
@@ -1647,7 +1898,19 @@
         <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R21" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S21" t="b">
+        <v>0</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -1674,19 +1937,19 @@
         <v>9.789999999999999</v>
       </c>
       <c r="G22" s="1" t="n">
-        <v>45219.55208333334</v>
+        <v>45222.38541666666</v>
       </c>
       <c r="H22" t="n">
-        <v>2627.8</v>
+        <v>2565.3</v>
       </c>
       <c r="I22" t="n">
         <v>2583.099666522532</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K22" t="n">
-        <v>1.26</v>
+        <v>-1.14</v>
       </c>
       <c r="L22" t="n">
         <v>3.47</v>
@@ -1695,7 +1958,7 @@
         <v>2.32</v>
       </c>
       <c r="N22" t="n">
-        <v>2.42</v>
+        <v>3.53</v>
       </c>
       <c r="O22" t="n">
         <v>4</v>
@@ -1704,7 +1967,19 @@
         <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="R22" s="3" t="n">
+        <v>45197</v>
+      </c>
+      <c r="S22" t="b">
+        <v>1</v>
+      </c>
+      <c r="T22" t="n">
+        <v>2</v>
+      </c>
+      <c r="U22" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="23">
@@ -1731,19 +2006,19 @@
         <v>6.43</v>
       </c>
       <c r="G23" s="1" t="n">
-        <v>45245.55208333334</v>
+        <v>45246.38541666666</v>
       </c>
       <c r="H23" t="n">
-        <v>2554</v>
+        <v>2608.6</v>
       </c>
       <c r="I23" t="n">
         <v>2604.393337887115</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K23" t="n">
-        <v>0.44</v>
+        <v>-1.69</v>
       </c>
       <c r="L23" t="n">
         <v>3.24</v>
@@ -1752,7 +2027,7 @@
         <v>2.08</v>
       </c>
       <c r="N23" t="n">
-        <v>4.31</v>
+        <v>4.54</v>
       </c>
       <c r="O23" t="n">
         <v>-3.53</v>
@@ -1761,7 +2036,19 @@
         <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R23" s="3" t="n">
+        <v>45225</v>
+      </c>
+      <c r="S23" t="b">
+        <v>1</v>
+      </c>
+      <c r="T23" t="n">
+        <v>2</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="24">
@@ -1788,28 +2075,28 @@
         <v>6.44</v>
       </c>
       <c r="G24" s="1" t="n">
-        <v>45301.55208333334</v>
+        <v>45302.38541666666</v>
       </c>
       <c r="H24" t="n">
-        <v>3158.7</v>
+        <v>2976.95</v>
       </c>
       <c r="I24" t="n">
         <v>3120.777488220217</v>
       </c>
       <c r="J24" s="2" t="n">
-        <v>55.16666666666666</v>
+        <v>56</v>
       </c>
       <c r="K24" t="n">
-        <v>21.09</v>
+        <v>14.12</v>
       </c>
       <c r="L24" t="n">
         <v>2.12</v>
       </c>
       <c r="M24" t="n">
-        <v>0.49</v>
+        <v>2.33</v>
       </c>
       <c r="N24" t="n">
-        <v>3.72</v>
+        <v>4.8</v>
       </c>
       <c r="O24" t="n">
         <v>4.54</v>
@@ -1818,7 +2105,19 @@
         <v>1</v>
       </c>
       <c r="Q24" t="n">
-        <v>76</v>
+        <v>77</v>
+      </c>
+      <c r="R24" s="3" t="n">
+        <v>45260</v>
+      </c>
+      <c r="S24" t="b">
+        <v>1</v>
+      </c>
+      <c r="T24" t="n">
+        <v>3</v>
+      </c>
+      <c r="U24" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="25">
@@ -1845,22 +2144,22 @@
         <v>10.17</v>
       </c>
       <c r="G25" s="1" t="n">
-        <v>45315.38541666666</v>
+        <v>45315.55208333334</v>
       </c>
       <c r="H25" t="n">
-        <v>3244.8</v>
+        <v>3313</v>
       </c>
       <c r="I25" t="n">
         <v>3248.626979684296</v>
       </c>
       <c r="J25" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K25" t="n">
-        <v>-9</v>
+        <v>-11.29</v>
       </c>
       <c r="L25" t="n">
-        <v>9.970000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="M25" t="n">
         <v>2.18</v>
@@ -1875,7 +2174,19 @@
         <v>1</v>
       </c>
       <c r="Q25" t="n">
-        <v>19</v>
+        <v>20</v>
+      </c>
+      <c r="R25" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S25" t="b">
+        <v>0</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1</v>
+      </c>
+      <c r="U25" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1902,28 +2213,28 @@
         <v>9.890000000000001</v>
       </c>
       <c r="G26" s="1" t="n">
-        <v>45363.55208333334</v>
+        <v>45364.38541666666</v>
       </c>
       <c r="H26" t="n">
-        <v>3278.3</v>
+        <v>3085</v>
       </c>
       <c r="I26" t="n">
         <v>3182.626293173764</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>48</v>
+        <v>48.83333333333334</v>
       </c>
       <c r="K26" t="n">
-        <v>-1.05</v>
+        <v>-6.88</v>
       </c>
       <c r="L26" t="n">
-        <v>8.24</v>
+        <v>8.48</v>
       </c>
       <c r="M26" t="n">
         <v>1.81</v>
       </c>
       <c r="N26" t="n">
-        <v>4.02</v>
+        <v>7.27</v>
       </c>
       <c r="O26" t="n">
         <v>10.99</v>
@@ -1932,7 +2243,19 @@
         <v>1</v>
       </c>
       <c r="Q26" t="n">
-        <v>64</v>
+        <v>65</v>
+      </c>
+      <c r="R26" s="3" t="n">
+        <v>45316</v>
+      </c>
+      <c r="S26" t="b">
+        <v>1</v>
+      </c>
+      <c r="T26" t="n">
+        <v>3</v>
+      </c>
+      <c r="U26" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="27">
@@ -1959,28 +2282,28 @@
         <v>11.83</v>
       </c>
       <c r="G27" s="1" t="n">
-        <v>45370.55208333334</v>
+        <v>45371.38541666666</v>
       </c>
       <c r="H27" t="n">
-        <v>3300</v>
+        <v>3393.25</v>
       </c>
       <c r="I27" t="n">
         <v>3344.884543893824</v>
       </c>
       <c r="J27" s="2" t="n">
-        <v>6.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K27" t="n">
-        <v>-6.97</v>
+        <v>-9.99</v>
       </c>
       <c r="L27" t="n">
-        <v>7.78</v>
+        <v>10.53</v>
       </c>
       <c r="M27" t="n">
         <v>0.58</v>
       </c>
       <c r="N27" t="n">
-        <v>3.69</v>
+        <v>3.76</v>
       </c>
       <c r="O27" t="n">
         <v>-7.27</v>
@@ -1989,7 +2312,19 @@
         <v>1</v>
       </c>
       <c r="Q27" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R27" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S27" t="b">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>1</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="28">
@@ -2016,19 +2351,19 @@
         <v>12.41</v>
       </c>
       <c r="G28" s="1" t="n">
-        <v>45446.55208333334</v>
+        <v>45447.38541666666</v>
       </c>
       <c r="H28" t="n">
-        <v>4214</v>
+        <v>3900</v>
       </c>
       <c r="I28" t="n">
         <v>4015.215619620161</v>
       </c>
       <c r="J28" s="2" t="n">
-        <v>75.16666666666667</v>
+        <v>76</v>
       </c>
       <c r="K28" t="n">
-        <v>24.19</v>
+        <v>14.93</v>
       </c>
       <c r="L28" t="n">
         <v>5.5</v>
@@ -2046,7 +2381,19 @@
         <v>0</v>
       </c>
       <c r="Q28" t="n">
-        <v>97</v>
+        <v>98</v>
+      </c>
+      <c r="R28" s="3" t="n">
+        <v>45379</v>
+      </c>
+      <c r="S28" t="b">
+        <v>1</v>
+      </c>
+      <c r="T28" t="n">
+        <v>4</v>
+      </c>
+      <c r="U28" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="29">
@@ -2073,28 +2420,28 @@
         <v>11.31</v>
       </c>
       <c r="G29" s="1" t="n">
-        <v>45450.55208333334</v>
+        <v>45453.38541666666</v>
       </c>
       <c r="H29" t="n">
-        <v>4213</v>
+        <v>4482.75</v>
       </c>
       <c r="I29" t="n">
         <v>4340.912600819854</v>
       </c>
       <c r="J29" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K29" t="n">
-        <v>-8.029999999999999</v>
+        <v>-14.94</v>
       </c>
       <c r="L29" t="n">
-        <v>10.23</v>
+        <v>15.36</v>
       </c>
       <c r="M29" t="n">
         <v>2.7</v>
       </c>
       <c r="N29" t="n">
-        <v>1.87</v>
+        <v>8</v>
       </c>
       <c r="O29" t="n">
         <v>-4.11</v>
@@ -2103,7 +2450,19 @@
         <v>1</v>
       </c>
       <c r="Q29" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R29" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S29" t="b">
+        <v>0</v>
+      </c>
+      <c r="T29" t="n">
+        <v>1</v>
+      </c>
+      <c r="U29" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="30">
@@ -2130,25 +2489,25 @@
         <v>12.8</v>
       </c>
       <c r="G30" s="1" t="n">
-        <v>45462.55208333334</v>
+        <v>45463.38541666666</v>
       </c>
       <c r="H30" t="n">
-        <v>4429.9</v>
+        <v>4345.15</v>
       </c>
       <c r="I30" t="n">
         <v>4373.699451446004</v>
       </c>
       <c r="J30" s="2" t="n">
-        <v>9.166666666666666</v>
+        <v>10</v>
       </c>
       <c r="K30" t="n">
-        <v>-1.18</v>
+        <v>-3.07</v>
       </c>
       <c r="L30" t="n">
         <v>4.75</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>0.22</v>
       </c>
       <c r="N30" t="n">
         <v>5.45</v>
@@ -2160,7 +2519,19 @@
         <v>1</v>
       </c>
       <c r="Q30" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R30" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S30" t="b">
+        <v>0</v>
+      </c>
+      <c r="T30" t="n">
+        <v>1</v>
+      </c>
+      <c r="U30" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="31">
@@ -2187,19 +2558,19 @@
         <v>10.86</v>
       </c>
       <c r="G31" s="1" t="n">
-        <v>45516.55208333334</v>
+        <v>45517.38541666666</v>
       </c>
       <c r="H31" t="n">
-        <v>4301.3</v>
+        <v>4331.6</v>
       </c>
       <c r="I31" t="n">
         <v>4314.131781168021</v>
       </c>
       <c r="J31" s="2" t="n">
-        <v>53.16666666666666</v>
+        <v>54</v>
       </c>
       <c r="K31" t="n">
-        <v>1.01</v>
+        <v>0.31</v>
       </c>
       <c r="L31" t="n">
         <v>9.779999999999999</v>
@@ -2217,7 +2588,19 @@
         <v>0</v>
       </c>
       <c r="Q31" t="n">
-        <v>74</v>
+        <v>75</v>
+      </c>
+      <c r="R31" s="3" t="n">
+        <v>45470</v>
+      </c>
+      <c r="S31" t="b">
+        <v>1</v>
+      </c>
+      <c r="T31" t="n">
+        <v>3</v>
+      </c>
+      <c r="U31" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="32">
@@ -2244,19 +2627,19 @@
         <v>7.07</v>
       </c>
       <c r="G32" s="1" t="n">
-        <v>45541.55208333334</v>
+        <v>45544.38541666666</v>
       </c>
       <c r="H32" t="n">
-        <v>4420</v>
+        <v>4358.3</v>
       </c>
       <c r="I32" t="n">
         <v>4394.008870182664</v>
       </c>
       <c r="J32" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K32" t="n">
-        <v>2.04</v>
+        <v>0.62</v>
       </c>
       <c r="L32" t="n">
         <v>2.99</v>
@@ -2274,7 +2657,19 @@
         <v>0</v>
       </c>
       <c r="Q32" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R32" s="3" t="n">
+        <v>45533</v>
+      </c>
+      <c r="S32" t="b">
+        <v>1</v>
+      </c>
+      <c r="T32" t="n">
+        <v>2</v>
+      </c>
+      <c r="U32" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="33">
@@ -2301,19 +2696,19 @@
         <v>5.43</v>
       </c>
       <c r="G33" s="1" t="n">
-        <v>45574.38541666666</v>
+        <v>45574.55208333334</v>
       </c>
       <c r="H33" t="n">
-        <v>4380</v>
+        <v>4390.6</v>
       </c>
       <c r="I33" t="n">
         <v>4386.746503792533</v>
       </c>
       <c r="J33" s="2" t="n">
-        <v>30</v>
+        <v>30.16666666666667</v>
       </c>
       <c r="K33" t="n">
-        <v>-0.5</v>
+        <v>-0.74</v>
       </c>
       <c r="L33" t="n">
         <v>5.13</v>
@@ -2331,7 +2726,19 @@
         <v>0</v>
       </c>
       <c r="Q33" t="n">
-        <v>43</v>
+        <v>44</v>
+      </c>
+      <c r="R33" s="3" t="n">
+        <v>45561</v>
+      </c>
+      <c r="S33" t="b">
+        <v>1</v>
+      </c>
+      <c r="T33" t="n">
+        <v>2</v>
+      </c>
+      <c r="U33" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="34">
@@ -2358,19 +2765,19 @@
         <v>7.12</v>
       </c>
       <c r="G34" s="1" t="n">
-        <v>45581.38541666666</v>
+        <v>45581.55208333334</v>
       </c>
       <c r="H34" t="n">
-        <v>4406.1</v>
+        <v>4355</v>
       </c>
       <c r="I34" t="n">
         <v>4373.546352279419</v>
       </c>
       <c r="J34" s="2" t="n">
-        <v>6.833333333333333</v>
+        <v>7</v>
       </c>
       <c r="K34" t="n">
-        <v>0.35</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="L34" t="n">
         <v>5.45</v>
@@ -2388,7 +2795,19 @@
         <v>1</v>
       </c>
       <c r="Q34" t="n">
-        <v>10</v>
+        <v>11</v>
+      </c>
+      <c r="R34" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S34" t="b">
+        <v>0</v>
+      </c>
+      <c r="T34" t="n">
+        <v>1</v>
+      </c>
+      <c r="U34" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -2415,19 +2834,19 @@
         <v>10.29</v>
       </c>
       <c r="G35" s="1" t="n">
-        <v>45617.55208333334</v>
+        <v>45618.38541666666</v>
       </c>
       <c r="H35" t="n">
-        <v>3790</v>
+        <v>3996.45</v>
       </c>
       <c r="I35" t="n">
         <v>3968.928633256679</v>
       </c>
       <c r="J35" s="2" t="n">
-        <v>36</v>
+        <v>36.83333333333334</v>
       </c>
       <c r="K35" t="n">
-        <v>12.97</v>
+        <v>8.23</v>
       </c>
       <c r="L35" t="n">
         <v>2.12</v>
@@ -2436,7 +2855,7 @@
         <v>1.49</v>
       </c>
       <c r="N35" t="n">
-        <v>4.82</v>
+        <v>5.41</v>
       </c>
       <c r="O35" t="n">
         <v>-7</v>
@@ -2445,7 +2864,19 @@
         <v>1</v>
       </c>
       <c r="Q35" t="n">
-        <v>48</v>
+        <v>49</v>
+      </c>
+      <c r="R35" s="3" t="n">
+        <v>45596</v>
+      </c>
+      <c r="S35" t="b">
+        <v>1</v>
+      </c>
+      <c r="T35" t="n">
+        <v>2</v>
+      </c>
+      <c r="U35" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="36">
@@ -2472,19 +2903,19 @@
         <v>10.01</v>
       </c>
       <c r="G36" s="1" t="n">
-        <v>45643.55208333334</v>
+        <v>45644.38541666666</v>
       </c>
       <c r="H36" t="n">
-        <v>4390</v>
+        <v>4302.25</v>
       </c>
       <c r="I36" t="n">
         <v>4318.647530972194</v>
       </c>
       <c r="J36" s="2" t="n">
-        <v>25.16666666666667</v>
+        <v>26</v>
       </c>
       <c r="K36" t="n">
-        <v>9.85</v>
+        <v>7.65</v>
       </c>
       <c r="L36" t="n">
         <v>5.52</v>
@@ -2502,7 +2933,19 @@
         <v>1</v>
       </c>
       <c r="Q36" t="n">
-        <v>36</v>
+        <v>37</v>
+      </c>
+      <c r="R36" s="3" t="n">
+        <v>45624</v>
+      </c>
+      <c r="S36" t="b">
+        <v>1</v>
+      </c>
+      <c r="T36" t="n">
+        <v>2</v>
+      </c>
+      <c r="U36" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="37">
@@ -2529,22 +2972,22 @@
         <v>7.25</v>
       </c>
       <c r="G37" s="1" t="n">
-        <v>45657.38541666666</v>
+        <v>45657.55208333334</v>
       </c>
       <c r="H37" t="n">
-        <v>4410.85</v>
+        <v>4429.9</v>
       </c>
       <c r="I37" t="n">
         <v>4424.479348446376</v>
       </c>
       <c r="J37" s="2" t="n">
-        <v>13</v>
+        <v>13.16666666666667</v>
       </c>
       <c r="K37" t="n">
-        <v>-2.52</v>
+        <v>-2.97</v>
       </c>
       <c r="L37" t="n">
-        <v>2.84</v>
+        <v>3.78</v>
       </c>
       <c r="M37" t="n">
         <v>2.5</v>
@@ -2559,7 +3002,19 @@
         <v>0</v>
       </c>
       <c r="Q37" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R37" s="3" t="n">
+        <v>45652</v>
+      </c>
+      <c r="S37" t="b">
+        <v>1</v>
+      </c>
+      <c r="T37" t="n">
+        <v>2</v>
+      </c>
+      <c r="U37" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="38">
@@ -2586,22 +3041,22 @@
         <v>5.32</v>
       </c>
       <c r="G38" s="1" t="n">
-        <v>45660.55208333334</v>
+        <v>45663.38541666666</v>
       </c>
       <c r="H38" t="n">
-        <v>4349.75</v>
+        <v>4250.45</v>
       </c>
       <c r="I38" t="n">
         <v>4261.623552902712</v>
       </c>
       <c r="J38" s="2" t="n">
-        <v>3</v>
+        <v>5.833333333333333</v>
       </c>
       <c r="K38" t="n">
-        <v>-1.81</v>
+        <v>-4.05</v>
       </c>
       <c r="L38" t="n">
-        <v>2.07</v>
+        <v>4.93</v>
       </c>
       <c r="M38" t="n">
         <v>-0</v>
@@ -2616,7 +3071,19 @@
         <v>0</v>
       </c>
       <c r="Q38" t="n">
-        <v>7</v>
+        <v>8</v>
+      </c>
+      <c r="R38" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S38" t="b">
+        <v>0</v>
+      </c>
+      <c r="T38" t="n">
+        <v>1</v>
+      </c>
+      <c r="U38" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -2643,28 +3110,28 @@
         <v>6.92</v>
       </c>
       <c r="G39" s="1" t="n">
-        <v>45679.55208333334</v>
+        <v>45680.38541666666</v>
       </c>
       <c r="H39" t="n">
-        <v>4109.4</v>
+        <v>4544.55</v>
       </c>
       <c r="I39" t="n">
         <v>4227.129093579957</v>
       </c>
       <c r="J39" s="2" t="n">
-        <v>16.16666666666667</v>
+        <v>17</v>
       </c>
       <c r="K39" t="n">
-        <v>3.32</v>
+        <v>-6.92</v>
       </c>
       <c r="L39" t="n">
-        <v>2.8</v>
+        <v>7.58</v>
       </c>
       <c r="M39" t="n">
         <v>0.7</v>
       </c>
       <c r="N39" t="n">
-        <v>1.72</v>
+        <v>8.529999999999999</v>
       </c>
       <c r="O39" t="n">
         <v>-1.6</v>
@@ -2673,7 +3140,19 @@
         <v>0</v>
       </c>
       <c r="Q39" t="n">
-        <v>26</v>
+        <v>27</v>
+      </c>
+      <c r="R39" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S39" t="b">
+        <v>0</v>
+      </c>
+      <c r="T39" t="n">
+        <v>1</v>
+      </c>
+      <c r="U39" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -2700,28 +3179,28 @@
         <v>13.63</v>
       </c>
       <c r="G40" s="1" t="n">
-        <v>45681.55208333334</v>
+        <v>45684.38541666666</v>
       </c>
       <c r="H40" t="n">
-        <v>4246.95</v>
+        <v>4032.95</v>
       </c>
       <c r="I40" t="n">
         <v>4107.174127349311</v>
       </c>
       <c r="J40" s="2" t="n">
-        <v>1.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K40" t="n">
-        <v>-6.55</v>
+        <v>-11.26</v>
       </c>
       <c r="L40" t="n">
-        <v>9.74</v>
+        <v>12.06</v>
       </c>
       <c r="M40" t="n">
-        <v>-0</v>
+        <v>1.51</v>
       </c>
       <c r="N40" t="n">
-        <v>4.78</v>
+        <v>6.03</v>
       </c>
       <c r="O40" t="n">
         <v>8.529999999999999</v>
@@ -2730,7 +3209,19 @@
         <v>1</v>
       </c>
       <c r="Q40" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R40" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S40" t="b">
+        <v>0</v>
+      </c>
+      <c r="T40" t="n">
+        <v>1</v>
+      </c>
+      <c r="U40" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -2757,19 +3248,19 @@
         <v>12.16</v>
       </c>
       <c r="G41" s="1" t="n">
-        <v>45707.55208333334</v>
+        <v>45708.38541666666</v>
       </c>
       <c r="H41" t="n">
-        <v>3574</v>
+        <v>3707.35</v>
       </c>
       <c r="I41" t="n">
         <v>3682.447046432274</v>
       </c>
       <c r="J41" s="2" t="n">
-        <v>23.16666666666667</v>
+        <v>24</v>
       </c>
       <c r="K41" t="n">
-        <v>11.38</v>
+        <v>8.07</v>
       </c>
       <c r="L41" t="n">
         <v>3.76</v>
@@ -2787,7 +3278,19 @@
         <v>1</v>
       </c>
       <c r="Q41" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R41" s="3" t="n">
+        <v>45687</v>
+      </c>
+      <c r="S41" t="b">
+        <v>1</v>
+      </c>
+      <c r="T41" t="n">
+        <v>2</v>
+      </c>
+      <c r="U41" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="42">
@@ -2814,28 +3317,28 @@
         <v>11.05</v>
       </c>
       <c r="G42" s="1" t="n">
-        <v>45713.55208333334</v>
+        <v>45715.38541666666</v>
       </c>
       <c r="H42" t="n">
-        <v>3775</v>
+        <v>3020.5</v>
       </c>
       <c r="I42" t="n">
         <v>3533.468661721986</v>
       </c>
       <c r="J42" s="2" t="n">
-        <v>5.166666666666667</v>
+        <v>7</v>
       </c>
       <c r="K42" t="n">
-        <v>1.82</v>
+        <v>-18.53</v>
       </c>
       <c r="L42" t="n">
-        <v>4.92</v>
+        <v>19.48</v>
       </c>
       <c r="M42" t="n">
-        <v>0.75</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="N42" t="n">
-        <v>2.32</v>
+        <v>21</v>
       </c>
       <c r="O42" t="n">
         <v>4.23</v>
@@ -2844,7 +3347,19 @@
         <v>1</v>
       </c>
       <c r="Q42" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R42" s="3" t="n">
+        <v>45715</v>
+      </c>
+      <c r="S42" t="b">
+        <v>0</v>
+      </c>
+      <c r="T42" t="n">
+        <v>1</v>
+      </c>
+      <c r="U42" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -2871,19 +3386,19 @@
         <v>23.32</v>
       </c>
       <c r="G43" s="1" t="n">
-        <v>45763.55208333334</v>
+        <v>45764.38541666666</v>
       </c>
       <c r="H43" t="n">
-        <v>2747.7</v>
+        <v>2849.5</v>
       </c>
       <c r="I43" t="n">
         <v>2752.261331528461</v>
       </c>
       <c r="J43" s="2" t="n">
-        <v>48.16666666666666</v>
+        <v>49</v>
       </c>
       <c r="K43" t="n">
-        <v>9.029999999999999</v>
+        <v>5.66</v>
       </c>
       <c r="L43" t="n">
         <v>14.22</v>
@@ -2901,7 +3416,19 @@
         <v>1</v>
       </c>
       <c r="Q43" t="n">
-        <v>60</v>
+        <v>61</v>
+      </c>
+      <c r="R43" s="3" t="n">
+        <v>45743</v>
+      </c>
+      <c r="S43" t="b">
+        <v>1</v>
+      </c>
+      <c r="T43" t="n">
+        <v>2</v>
+      </c>
+      <c r="U43" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="44">
@@ -2928,19 +3455,19 @@
         <v>8.58</v>
       </c>
       <c r="G44" s="1" t="n">
-        <v>45824.55208333334</v>
+        <v>45825.38541666666</v>
       </c>
       <c r="H44" t="n">
-        <v>3689.9</v>
+        <v>3613.4</v>
       </c>
       <c r="I44" t="n">
         <v>3648.326540217084</v>
       </c>
       <c r="J44" s="2" t="n">
-        <v>60.16666666666666</v>
+        <v>61</v>
       </c>
       <c r="K44" t="n">
-        <v>29.49</v>
+        <v>26.81</v>
       </c>
       <c r="L44" t="n">
         <v>2.35</v>
@@ -2958,7 +3485,19 @@
         <v>0</v>
       </c>
       <c r="Q44" t="n">
-        <v>82</v>
+        <v>83</v>
+      </c>
+      <c r="R44" s="3" t="n">
+        <v>45771</v>
+      </c>
+      <c r="S44" t="b">
+        <v>1</v>
+      </c>
+      <c r="T44" t="n">
+        <v>3</v>
+      </c>
+      <c r="U44" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="45">
@@ -2985,28 +3524,28 @@
         <v>6.53</v>
       </c>
       <c r="G45" s="1" t="n">
-        <v>45828.55208333334</v>
+        <v>45831.38541666666</v>
       </c>
       <c r="H45" t="n">
-        <v>3570.4</v>
+        <v>3778.6</v>
       </c>
       <c r="I45" t="n">
         <v>3749.163149655083</v>
       </c>
       <c r="J45" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>6</v>
       </c>
       <c r="K45" t="n">
-        <v>1.19</v>
+        <v>-4.57</v>
       </c>
       <c r="L45" t="n">
-        <v>2.39</v>
+        <v>5.36</v>
       </c>
       <c r="M45" t="n">
         <v>0.1</v>
       </c>
       <c r="N45" t="n">
-        <v>0.14</v>
+        <v>5.22</v>
       </c>
       <c r="O45" t="n">
         <v>-1.89</v>
@@ -3015,7 +3554,19 @@
         <v>0</v>
       </c>
       <c r="Q45" t="n">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S45" t="b">
+        <v>0</v>
+      </c>
+      <c r="T45" t="n">
+        <v>1</v>
+      </c>
+      <c r="U45" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -3042,19 +3593,19 @@
         <v>9.43</v>
       </c>
       <c r="G46" s="1" t="n">
-        <v>45848.55208333334</v>
+        <v>45849.38541666666</v>
       </c>
       <c r="H46" t="n">
-        <v>3700</v>
+        <v>3643.1</v>
       </c>
       <c r="I46" t="n">
         <v>3645.41674619508</v>
       </c>
       <c r="J46" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K46" t="n">
-        <v>-2.08</v>
+        <v>-3.59</v>
       </c>
       <c r="L46" t="n">
         <v>6.7</v>
@@ -3063,7 +3614,7 @@
         <v>0.83</v>
       </c>
       <c r="N46" t="n">
-        <v>2</v>
+        <v>2.44</v>
       </c>
       <c r="O46" t="n">
         <v>5.22</v>
@@ -3072,7 +3623,19 @@
         <v>1</v>
       </c>
       <c r="Q46" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R46" s="3" t="n">
+        <v>45834</v>
+      </c>
+      <c r="S46" t="b">
+        <v>1</v>
+      </c>
+      <c r="T46" t="n">
+        <v>2</v>
+      </c>
+      <c r="U46" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="47">
@@ -3099,28 +3662,28 @@
         <v>5.45</v>
       </c>
       <c r="G47" s="1" t="n">
-        <v>45852.55208333334</v>
+        <v>45853.38541666666</v>
       </c>
       <c r="H47" t="n">
-        <v>3741</v>
+        <v>3846.6</v>
       </c>
       <c r="I47" t="n">
         <v>3801.215037719948</v>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.166666666666667</v>
+        <v>4</v>
       </c>
       <c r="K47" t="n">
-        <v>-2.69</v>
+        <v>-5.59</v>
       </c>
       <c r="L47" t="n">
-        <v>3.07</v>
+        <v>5.82</v>
       </c>
       <c r="M47" t="n">
         <v>1.11</v>
       </c>
       <c r="N47" t="n">
-        <v>3.63</v>
+        <v>4.15</v>
       </c>
       <c r="O47" t="n">
         <v>-2.44</v>
@@ -3129,7 +3692,19 @@
         <v>0</v>
       </c>
       <c r="Q47" t="n">
-        <v>4</v>
+        <v>5</v>
+      </c>
+      <c r="R47" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S47" t="b">
+        <v>0</v>
+      </c>
+      <c r="T47" t="n">
+        <v>1</v>
+      </c>
+      <c r="U47" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -3156,22 +3731,22 @@
         <v>6.49</v>
       </c>
       <c r="G48" s="1" t="n">
-        <v>45874.55208333334</v>
+        <v>45875.38541666666</v>
       </c>
       <c r="H48" t="n">
-        <v>3815.8</v>
+        <v>3762.9</v>
       </c>
       <c r="I48" t="n">
         <v>3779.421109643603</v>
       </c>
       <c r="J48" s="2" t="n">
-        <v>21.16666666666667</v>
+        <v>22</v>
       </c>
       <c r="K48" t="n">
-        <v>-0.8</v>
+        <v>-2.18</v>
       </c>
       <c r="L48" t="n">
-        <v>2.54</v>
+        <v>3.12</v>
       </c>
       <c r="M48" t="n">
         <v>1.15</v>
@@ -3186,7 +3761,19 @@
         <v>1</v>
       </c>
       <c r="Q48" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R48" s="3" t="n">
+        <v>45869</v>
+      </c>
+      <c r="S48" t="b">
+        <v>1</v>
+      </c>
+      <c r="T48" t="n">
+        <v>2</v>
+      </c>
+      <c r="U48" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="49">
@@ -3213,22 +3800,22 @@
         <v>5.89</v>
       </c>
       <c r="G49" s="1" t="n">
-        <v>45888.55208333334</v>
+        <v>45889.38541666666</v>
       </c>
       <c r="H49" t="n">
-        <v>3962</v>
+        <v>4015.2</v>
       </c>
       <c r="I49" t="n">
         <v>3963.949902685421</v>
       </c>
       <c r="J49" s="2" t="n">
-        <v>13.16666666666667</v>
+        <v>14</v>
       </c>
       <c r="K49" t="n">
-        <v>-5.29</v>
+        <v>-6.7</v>
       </c>
       <c r="L49" t="n">
-        <v>5.57</v>
+        <v>8.4</v>
       </c>
       <c r="M49" t="n">
         <v>0.45</v>
@@ -3243,7 +3830,19 @@
         <v>0</v>
       </c>
       <c r="Q49" t="n">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="R49" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S49" t="b">
+        <v>0</v>
+      </c>
+      <c r="T49" t="n">
+        <v>1</v>
+      </c>
+      <c r="U49" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="50">
@@ -3270,19 +3869,19 @@
         <v>6.03</v>
       </c>
       <c r="G50" s="1" t="n">
-        <v>45926.55208333334</v>
+        <v>45929.38541666666</v>
       </c>
       <c r="H50" t="n">
-        <v>4060</v>
+        <v>4019.1</v>
       </c>
       <c r="I50" t="n">
         <v>4027.32228777647</v>
       </c>
       <c r="J50" s="2" t="n">
-        <v>37.16666666666666</v>
+        <v>40</v>
       </c>
       <c r="K50" t="n">
-        <v>1.12</v>
+        <v>0.1</v>
       </c>
       <c r="L50" t="n">
         <v>5.78</v>
@@ -3300,7 +3899,19 @@
         <v>0</v>
       </c>
       <c r="Q50" t="n">
-        <v>54</v>
+        <v>55</v>
+      </c>
+      <c r="R50" s="3" t="n">
+        <v>45897</v>
+      </c>
+      <c r="S50" t="b">
+        <v>1</v>
+      </c>
+      <c r="T50" t="n">
+        <v>2</v>
+      </c>
+      <c r="U50" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="51">
@@ -3327,22 +3938,22 @@
         <v>6.83</v>
       </c>
       <c r="G51" s="1" t="n">
-        <v>45937.55208333334</v>
+        <v>45938.38541666666</v>
       </c>
       <c r="H51" t="n">
-        <v>4209</v>
+        <v>4271.5</v>
       </c>
       <c r="I51" t="n">
         <v>4240.637359783213</v>
       </c>
       <c r="J51" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K51" t="n">
-        <v>-4.72</v>
+        <v>-6.28</v>
       </c>
       <c r="L51" t="n">
-        <v>4.84</v>
+        <v>6.49</v>
       </c>
       <c r="M51" t="n">
         <v>0.49</v>
@@ -3357,7 +3968,19 @@
         <v>0</v>
       </c>
       <c r="Q51" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R51" s="3" t="n">
+        <v>45930</v>
+      </c>
+      <c r="S51" t="b">
+        <v>1</v>
+      </c>
+      <c r="T51" t="n">
+        <v>2</v>
+      </c>
+      <c r="U51" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="52">
@@ -3384,28 +4007,28 @@
         <v>6.3</v>
       </c>
       <c r="G52" s="1" t="n">
-        <v>45945.55208333334</v>
+        <v>45946.38541666666</v>
       </c>
       <c r="H52" t="n">
-        <v>4446.1</v>
+        <v>4147</v>
       </c>
       <c r="I52" t="n">
         <v>4182.589066017081</v>
       </c>
       <c r="J52" s="2" t="n">
-        <v>7.166666666666667</v>
+        <v>8</v>
       </c>
       <c r="K52" t="n">
-        <v>4.09</v>
+        <v>-2.91</v>
       </c>
       <c r="L52" t="n">
-        <v>2.37</v>
+        <v>5.61</v>
       </c>
       <c r="M52" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="N52" t="n">
-        <v>0.24</v>
+        <v>6.21</v>
       </c>
       <c r="O52" t="n">
         <v>0.97</v>
@@ -3414,7 +4037,19 @@
         <v>0</v>
       </c>
       <c r="Q52" t="n">
-        <v>12</v>
+        <v>13</v>
+      </c>
+      <c r="R52" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S52" t="b">
+        <v>0</v>
+      </c>
+      <c r="T52" t="n">
+        <v>1</v>
+      </c>
+      <c r="U52" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -3441,19 +4076,19 @@
         <v>9.92</v>
       </c>
       <c r="G53" s="1" t="n">
-        <v>45972.55208333334</v>
+        <v>45973.38541666666</v>
       </c>
       <c r="H53" t="n">
-        <v>4064.9</v>
+        <v>4083.3</v>
       </c>
       <c r="I53" t="n">
         <v>4076.527620973081</v>
       </c>
       <c r="J53" s="2" t="n">
-        <v>26.16666666666667</v>
+        <v>27</v>
       </c>
       <c r="K53" t="n">
-        <v>1.98</v>
+        <v>1.54</v>
       </c>
       <c r="L53" t="n">
         <v>6.94</v>
@@ -3471,7 +4106,19 @@
         <v>1</v>
       </c>
       <c r="Q53" t="n">
-        <v>33</v>
+        <v>34</v>
+      </c>
+      <c r="R53" s="3" t="n">
+        <v>45958</v>
+      </c>
+      <c r="S53" t="b">
+        <v>1</v>
+      </c>
+      <c r="T53" t="n">
+        <v>2</v>
+      </c>
+      <c r="U53" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="54">
@@ -3498,19 +4145,19 @@
         <v>3.94</v>
       </c>
       <c r="G54" s="1" t="n">
-        <v>46000.55208333334</v>
+        <v>46001.38541666666</v>
       </c>
       <c r="H54" t="n">
-        <v>4069.1</v>
+        <v>3992.5</v>
       </c>
       <c r="I54" t="n">
         <v>4026.958465752934</v>
       </c>
       <c r="J54" s="2" t="n">
-        <v>27.16666666666667</v>
+        <v>28</v>
       </c>
       <c r="K54" t="n">
-        <v>-0.35</v>
+        <v>-2.22</v>
       </c>
       <c r="L54" t="n">
         <v>2.36</v>
@@ -3519,7 +4166,7 @@
         <v>0.64</v>
       </c>
       <c r="N54" t="n">
-        <v>2.36</v>
+        <v>3.37</v>
       </c>
       <c r="O54" t="n">
         <v>0.13</v>
@@ -3528,7 +4175,19 @@
         <v>0</v>
       </c>
       <c r="Q54" t="n">
-        <v>40</v>
+        <v>41</v>
+      </c>
+      <c r="R54" s="3" t="n">
+        <v>45986</v>
+      </c>
+      <c r="S54" t="b">
+        <v>1</v>
+      </c>
+      <c r="T54" t="n">
+        <v>2</v>
+      </c>
+      <c r="U54" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="55">
@@ -3555,19 +4214,19 @@
         <v>6.4</v>
       </c>
       <c r="G55" s="1" t="n">
-        <v>46009.55208333334</v>
+        <v>46010.38541666666</v>
       </c>
       <c r="H55" t="n">
-        <v>4099</v>
+        <v>4182.4</v>
       </c>
       <c r="I55" t="n">
         <v>4179.903098453427</v>
       </c>
       <c r="J55" s="2" t="n">
-        <v>8.166666666666666</v>
+        <v>9</v>
       </c>
       <c r="K55" t="n">
-        <v>-2.67</v>
+        <v>-4.76</v>
       </c>
       <c r="L55" t="n">
         <v>5.17</v>
@@ -3576,7 +4235,7 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="N55" t="n">
-        <v>2.87</v>
+        <v>4.54</v>
       </c>
       <c r="O55" t="n">
         <v>-3.37</v>
@@ -3585,7 +4244,19 @@
         <v>0</v>
       </c>
       <c r="Q55" t="n">
-        <v>14</v>
+        <v>15</v>
+      </c>
+      <c r="R55" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S55" t="b">
+        <v>0</v>
+      </c>
+      <c r="T55" t="n">
+        <v>1</v>
+      </c>
+      <c r="U55" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="56">
@@ -3612,19 +4283,19 @@
         <v>5.7</v>
       </c>
       <c r="G56" s="1" t="n">
-        <v>46030.55208333334</v>
+        <v>46031.38541666666</v>
       </c>
       <c r="H56" t="n">
-        <v>4401</v>
+        <v>4350.3</v>
       </c>
       <c r="I56" t="n">
         <v>4366.702444234932</v>
       </c>
       <c r="J56" s="2" t="n">
-        <v>20.16666666666667</v>
+        <v>21</v>
       </c>
       <c r="K56" t="n">
-        <v>5.23</v>
+        <v>4.01</v>
       </c>
       <c r="L56" t="n">
         <v>2.25</v>
@@ -3642,7 +4313,19 @@
         <v>1</v>
       </c>
       <c r="Q56" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R56" s="3" t="n">
+        <v>46021</v>
+      </c>
+      <c r="S56" t="b">
+        <v>1</v>
+      </c>
+      <c r="T56" t="n">
+        <v>2</v>
+      </c>
+      <c r="U56" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="57">
@@ -3669,28 +4352,28 @@
         <v>5.48</v>
       </c>
       <c r="G57" s="1" t="n">
-        <v>46055.55208333334</v>
+        <v>46056.38541666666</v>
       </c>
       <c r="H57" t="n">
-        <v>4073.6</v>
+        <v>4318.4</v>
       </c>
       <c r="I57" t="n">
         <v>4114.956516396338</v>
       </c>
       <c r="J57" s="2" t="n">
-        <v>24.16666666666667</v>
+        <v>25</v>
       </c>
       <c r="K57" t="n">
-        <v>6.36</v>
+        <v>0.73</v>
       </c>
       <c r="L57" t="n">
-        <v>2.25</v>
+        <v>4.82</v>
       </c>
       <c r="M57" t="n">
-        <v>1.13</v>
+        <v>5.56</v>
       </c>
       <c r="N57" t="n">
-        <v>4.02</v>
+        <v>6.96</v>
       </c>
       <c r="O57" t="n">
         <v>-1.7</v>
@@ -3699,7 +4382,19 @@
         <v>0</v>
       </c>
       <c r="Q57" t="n">
-        <v>32</v>
+        <v>33</v>
+      </c>
+      <c r="R57" s="3" t="n">
+        <v>46049</v>
+      </c>
+      <c r="S57" t="b">
+        <v>1</v>
+      </c>
+      <c r="T57" t="n">
+        <v>2</v>
+      </c>
+      <c r="U57" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="58">
@@ -3726,19 +4421,19 @@
         <v>7.62</v>
       </c>
       <c r="G58" s="1" t="n">
-        <v>46087.55208333334</v>
+        <v>46090.38541666666</v>
       </c>
       <c r="H58" t="n">
-        <v>4930</v>
+        <v>4687</v>
       </c>
       <c r="I58" t="n">
         <v>4779.165204870086</v>
       </c>
       <c r="J58" s="2" t="n">
-        <v>31.16666666666667</v>
+        <v>34</v>
       </c>
       <c r="K58" t="n">
-        <v>14.16</v>
+        <v>8.539999999999999</v>
       </c>
       <c r="L58" t="n">
         <v>0.84</v>
@@ -3756,7 +4451,19 @@
         <v>1</v>
       </c>
       <c r="Q58" t="n">
-        <v>46</v>
+        <v>47</v>
+      </c>
+      <c r="R58" s="3" t="n">
+        <v>46077</v>
+      </c>
+      <c r="S58" t="b">
+        <v>1</v>
+      </c>
+      <c r="T58" t="n">
+        <v>2</v>
+      </c>
+      <c r="U58" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
@@ -3783,28 +4490,28 @@
         <v>10.46</v>
       </c>
       <c r="G59" s="1" t="n">
-        <v>46119.55208333334</v>
+        <v>46120.38541666666</v>
       </c>
       <c r="H59" t="n">
-        <v>4240</v>
+        <v>4517</v>
       </c>
       <c r="I59" t="n">
         <v>4348.804069583413</v>
       </c>
       <c r="J59" s="2" t="n">
-        <v>29.16666666666667</v>
+        <v>30</v>
       </c>
       <c r="K59" t="n">
-        <v>9.539999999999999</v>
+        <v>3.63</v>
       </c>
       <c r="L59" t="n">
         <v>4.01</v>
       </c>
       <c r="M59" t="n">
-        <v>3.51</v>
+        <v>4.95</v>
       </c>
       <c r="N59" t="n">
-        <v>3.58</v>
+        <v>6.13</v>
       </c>
       <c r="O59" t="n">
         <v>-2.64</v>
@@ -3813,7 +4520,19 @@
         <v>0</v>
       </c>
       <c r="Q59" t="n">
-        <v>38</v>
+        <v>39</v>
+      </c>
+      <c r="R59" s="3" t="n">
+        <v>46111</v>
+      </c>
+      <c r="S59" t="b">
+        <v>1</v>
+      </c>
+      <c r="T59" t="n">
+        <v>2</v>
+      </c>
+      <c r="U59" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="60">
@@ -3840,19 +4559,19 @@
         <v>9.5</v>
       </c>
       <c r="G60" s="1" t="n">
-        <v>46181.38541666666</v>
+        <v>46181.55208333334</v>
       </c>
       <c r="H60" t="n">
-        <v>5239</v>
+        <v>5111</v>
       </c>
       <c r="I60" t="n">
         <v>5164.438315816553</v>
       </c>
       <c r="J60" s="2" t="n">
-        <v>61</v>
+        <v>61.16666666666666</v>
       </c>
       <c r="K60" t="n">
-        <v>15.98</v>
+        <v>13.15</v>
       </c>
       <c r="L60" t="n">
         <v>4.78</v>
@@ -3870,7 +4589,19 @@
         <v>1</v>
       </c>
       <c r="Q60" t="n">
-        <v>81</v>
+        <v>82</v>
+      </c>
+      <c r="R60" s="3" t="n">
+        <v>46140</v>
+      </c>
+      <c r="S60" t="b">
+        <v>1</v>
+      </c>
+      <c r="T60" t="n">
+        <v>3</v>
+      </c>
+      <c r="U60" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="61">
@@ -3897,22 +4628,22 @@
         <v>7.71</v>
       </c>
       <c r="G61" s="1" t="n">
-        <v>46185.55208333334</v>
+        <v>46188.38541666666</v>
       </c>
       <c r="H61" t="n">
-        <v>5367</v>
+        <v>5512.5</v>
       </c>
       <c r="I61" t="n">
         <v>5504.916808936942</v>
       </c>
       <c r="J61" s="2" t="n">
-        <v>4</v>
+        <v>6.833333333333333</v>
       </c>
       <c r="K61" t="n">
-        <v>-5.01</v>
+        <v>-7.86</v>
       </c>
       <c r="L61" t="n">
-        <v>5.32</v>
+        <v>7.9</v>
       </c>
       <c r="M61" t="n">
         <v>2.09</v>
@@ -3927,7 +4658,19 @@
         <v>1</v>
       </c>
       <c r="Q61" t="n">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="R61" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S61" t="b">
+        <v>0</v>
+      </c>
+      <c r="T61" t="n">
+        <v>1</v>
+      </c>
+      <c r="U61" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3954,22 +4697,22 @@
         <v>7.37</v>
       </c>
       <c r="G62" s="1" t="n">
-        <v>46198.38541666666</v>
+        <v>46198.55208333334</v>
       </c>
       <c r="H62" t="n">
-        <v>5385</v>
+        <v>5261</v>
       </c>
       <c r="I62" t="n">
         <v>5335.501914462664</v>
       </c>
       <c r="J62" s="2" t="n">
-        <v>10</v>
+        <v>10.16666666666667</v>
       </c>
       <c r="K62" t="n">
-        <v>-2.31</v>
+        <v>-4.56</v>
       </c>
       <c r="L62" t="n">
-        <v>4.55</v>
+        <v>5.12</v>
       </c>
       <c r="M62" t="n">
         <v>0.03</v>
@@ -3984,7 +4727,19 @@
         <v>0</v>
       </c>
       <c r="Q62" t="n">
-        <v>17</v>
+        <v>18</v>
+      </c>
+      <c r="R62" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S62" t="b">
+        <v>0</v>
+      </c>
+      <c r="T62" t="n">
+        <v>1</v>
+      </c>
+      <c r="U62" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="63">
@@ -4011,19 +4766,19 @@
         <v>7.99</v>
       </c>
       <c r="G63" s="1" t="n">
-        <v>46234.55208333334</v>
+        <v>46237.38541666666</v>
       </c>
       <c r="H63" t="n">
-        <v>4993</v>
+        <v>5044.5</v>
       </c>
       <c r="I63" t="n">
         <v>5013.281634818895</v>
       </c>
       <c r="J63" s="2" t="n">
-        <v>36</v>
+        <v>38.83333333333334</v>
       </c>
       <c r="K63" t="n">
-        <v>5.09</v>
+        <v>4.12</v>
       </c>
       <c r="L63" t="n">
         <v>6.44</v>
@@ -4041,7 +4796,19 @@
         <v>0</v>
       </c>
       <c r="Q63" t="n">
-        <v>51</v>
+        <v>52</v>
+      </c>
+      <c r="R63" s="3" t="n">
+        <v>46203</v>
+      </c>
+      <c r="S63" t="b">
+        <v>1</v>
+      </c>
+      <c r="T63" t="n">
+        <v>3</v>
+      </c>
+      <c r="U63" t="n">
+        <v>2</v>
       </c>
     </row>
     <row r="64">
@@ -4068,19 +4835,19 @@
         <v>6.19</v>
       </c>
       <c r="G64" s="1" t="n">
-        <v>46254.55208333334</v>
+        <v>46255.38541666666</v>
       </c>
       <c r="H64" t="n">
-        <v>5671.4</v>
+        <v>5545.7</v>
       </c>
       <c r="I64" t="n">
         <v>5552.759634051984</v>
       </c>
       <c r="J64" s="2" t="n">
-        <v>17.16666666666667</v>
+        <v>18</v>
       </c>
       <c r="K64" t="n">
-        <v>12.43</v>
+        <v>9.94</v>
       </c>
       <c r="L64" t="n">
         <v>1.61</v>
@@ -4089,7 +4856,7 @@
         <v>0.29</v>
       </c>
       <c r="N64" t="n">
-        <v>1.59</v>
+        <v>2.7</v>
       </c>
       <c r="O64" t="n">
         <v>0.6</v>
@@ -4098,7 +4865,19 @@
         <v>0</v>
       </c>
       <c r="Q64" t="n">
-        <v>28</v>
+        <v>29</v>
+      </c>
+      <c r="R64" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S64" t="b">
+        <v>0</v>
+      </c>
+      <c r="T64" t="n">
+        <v>1</v>
+      </c>
+      <c r="U64" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="65">
@@ -4149,6 +4928,14 @@
       <c r="Q65" t="n">
         <v>90</v>
       </c>
+      <c r="R65" s="3" t="n">
+        <v>46259</v>
+      </c>
+      <c r="S65" t="b">
+        <v>1</v>
+      </c>
+      <c r="T65" t="inlineStr"/>
+      <c r="U65" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6251,7 +7038,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>25.5</v>
+        <v>26.7</v>
       </c>
     </row>
     <row r="6">
@@ -6261,7 +7048,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>20.2</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7">
@@ -6271,7 +7058,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>121.2</v>
+        <v>124</v>
       </c>
     </row>
     <row r="8">
@@ -6281,7 +7068,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1.2</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -6291,7 +7078,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>32</v>
+        <v>33.5</v>
       </c>
     </row>
     <row r="10">
@@ -6301,7 +7088,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>54.8</v>
+        <v>55.6</v>
       </c>
     </row>
     <row r="11">
@@ -6311,7 +7098,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12">
@@ -6321,7 +7108,7 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13">
@@ -6331,7 +7118,7 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>73</v>
+        <v>71.40000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -6341,7 +7128,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.59</v>
+        <v>0.17</v>
       </c>
     </row>
     <row r="15">
@@ -6351,7 +7138,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>6.81</v>
+        <v>3.07</v>
       </c>
     </row>
     <row r="16">
@@ -6361,7 +7148,7 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.26</v>
+        <v>-2.83</v>
       </c>
     </row>
     <row r="17">
@@ -6371,7 +7158,7 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>41.66</v>
+        <v>39.8</v>
       </c>
     </row>
     <row r="18">
@@ -6381,7 +7168,7 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>58.7</v>
+        <v>42.9</v>
       </c>
     </row>
     <row r="19">
@@ -6391,7 +7178,7 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>4.8</v>
+        <v>5.99</v>
       </c>
     </row>
     <row r="20">
@@ -6401,7 +7188,7 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>4.78</v>
+        <v>5.45</v>
       </c>
     </row>
     <row r="21">
@@ -6411,7 +7198,7 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>14.22</v>
+        <v>19.48</v>
       </c>
     </row>
     <row r="22">
@@ -6421,7 +7208,7 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
     </row>
     <row r="23">
@@ -6431,7 +7218,7 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24">
@@ -6441,7 +7228,7 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1.38</v>
+        <v>1.73</v>
       </c>
     </row>
     <row r="25">
@@ -6451,7 +7238,7 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4.29</v>
+        <v>8.609999999999999</v>
       </c>
     </row>
     <row r="26">
@@ -6461,7 +7248,7 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>3.6</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="27">
@@ -6471,7 +7258,7 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>10.99</v>
+        <v>21</v>
       </c>
     </row>
     <row r="28">
@@ -6481,7 +7268,7 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>23</v>
+        <v>35</v>
       </c>
     </row>
     <row r="29">
